--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135522442</v>
+        <v>135494432</v>
       </c>
       <c r="B2" t="n">
-        <v>93271</v>
+        <v>92027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>852302</v>
+        <v>852076</v>
       </c>
       <c r="R2" t="n">
-        <v>7375398</v>
+        <v>7375438</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135522447</v>
+        <v>135494433</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>93263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>852110</v>
+        <v>852036</v>
       </c>
       <c r="R3" t="n">
-        <v>7375452</v>
+        <v>7375427</v>
       </c>
       <c r="S3" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135522448</v>
+        <v>135494436</v>
       </c>
       <c r="B4" t="n">
-        <v>93271</v>
+        <v>93263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>852103</v>
+        <v>852153</v>
       </c>
       <c r="R4" t="n">
-        <v>7375422</v>
+        <v>7375385</v>
       </c>
       <c r="S4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135522430</v>
+        <v>135494440</v>
       </c>
       <c r="B5" t="n">
-        <v>93283</v>
+        <v>93263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>852692</v>
+        <v>852441</v>
       </c>
       <c r="R5" t="n">
-        <v>7375409</v>
+        <v>7375422</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135522445</v>
+        <v>135494391</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>852123</v>
+        <v>852813</v>
       </c>
       <c r="R6" t="n">
-        <v>7375442</v>
+        <v>7375454</v>
       </c>
       <c r="S6" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135522443</v>
+        <v>135494392</v>
       </c>
       <c r="B7" t="n">
-        <v>79992</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1221,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>852263</v>
+        <v>852798</v>
       </c>
       <c r="R7" t="n">
-        <v>7375416</v>
+        <v>7375455</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1293,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp, ny fruktkropp och vit mycelmatta</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,28 +1307,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135522444</v>
+        <v>135494394</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>852196</v>
+        <v>852754</v>
       </c>
       <c r="R8" t="n">
-        <v>7375416</v>
+        <v>7375447</v>
       </c>
       <c r="S8" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,22 +1421,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135522449</v>
+        <v>135494395</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>852030</v>
+        <v>852741</v>
       </c>
       <c r="R9" t="n">
-        <v>7375425</v>
+        <v>7375423</v>
       </c>
       <c r="S9" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,22 +1528,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135522446</v>
+        <v>135494396</v>
       </c>
       <c r="B10" t="n">
-        <v>79396</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>260591</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1575,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>852123</v>
+        <v>852725</v>
       </c>
       <c r="R10" t="n">
-        <v>7375442</v>
+        <v>7375423</v>
       </c>
       <c r="S10" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,15 +1635,3132 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135494397</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>852740</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7375427</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135494404</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>852689</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7375444</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135494405</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>852695</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7375470</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135494408</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>852761</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7375492</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135494435</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>852119</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7375379</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135522442</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>852302</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7375398</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Elin Kannerby</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135522447</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>852110</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7375452</v>
+      </c>
+      <c r="S17" t="n">
+        <v>51</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135522448</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>852103</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7375422</v>
+      </c>
+      <c r="S18" t="n">
+        <v>19</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135494439</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93275</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>852377</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7375395</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Under kolad stubbe med markkontakt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135522430</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93283</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>852692</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7375409</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135494410</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92915</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>852758</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7375446</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135494430</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>852122</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135522445</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>852123</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S23" t="n">
+        <v>64</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135494402</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>852696</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7375404</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135494411</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>852712</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7375445</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135494431</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>852101</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7375449</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135522443</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>852263</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7375416</v>
+      </c>
+      <c r="S27" t="n">
+        <v>32</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135494438</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>852178</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7375380</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135522444</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>852196</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7375416</v>
+      </c>
+      <c r="S29" t="n">
+        <v>64</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135522449</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>852030</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7375425</v>
+      </c>
+      <c r="S30" t="n">
+        <v>41</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135494429</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>852147</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7375437</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135494393</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>852762</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7375449</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135494406</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>852733</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7375489</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135494409</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>852761</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7375492</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135494412</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>852548</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7375432</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135494413</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>852548</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7375398</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135494427</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>852235</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7375410</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135494428</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>852154</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135522446</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>852123</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S39" t="n">
+        <v>68</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494432</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494433</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494440</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494392</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494394</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494395</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494396</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494397</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494404</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494405</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494408</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494435</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522442</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522447</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522448</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494439</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522430</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2830,6 +2930,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494410</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2937,6 +3042,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494430</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3044,6 +3154,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522445</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3151,6 +3266,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494402</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3258,6 +3378,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494411</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3365,6 +3490,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494431</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3472,6 +3602,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522443</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3584,6 +3719,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494438</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3691,6 +3831,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522444</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3798,6 +3943,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522449</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3905,6 +4055,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494429</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4012,6 +4167,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494393</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4119,6 +4279,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494406</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4226,6 +4391,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494409</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4333,6 +4503,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494412</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4440,6 +4615,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494413</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4547,6 +4727,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494427</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4654,6 +4839,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494428</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4761,8 +4951,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135494432</v>
       </c>
       <c r="B2" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135494433</v>
       </c>
       <c r="B3" t="n">
-        <v>93263</v>
+        <v>93305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135494436</v>
       </c>
       <c r="B4" t="n">
-        <v>93263</v>
+        <v>93305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135494440</v>
       </c>
       <c r="B5" t="n">
-        <v>93263</v>
+        <v>93305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135494391</v>
       </c>
       <c r="B6" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135494392</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135494394</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>135494395</v>
       </c>
       <c r="B9" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135494396</v>
       </c>
       <c r="B10" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>135494397</v>
       </c>
       <c r="B11" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>135494404</v>
       </c>
       <c r="B12" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135494405</v>
       </c>
       <c r="B13" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>135494408</v>
       </c>
       <c r="B14" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135494435</v>
       </c>
       <c r="B15" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135522442</v>
       </c>
       <c r="B16" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135522447</v>
       </c>
       <c r="B17" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135522448</v>
       </c>
       <c r="B18" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135494439</v>
       </c>
       <c r="B19" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>135522430</v>
       </c>
       <c r="B20" t="n">
-        <v>93283</v>
+        <v>93325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135494410</v>
       </c>
       <c r="B21" t="n">
-        <v>92915</v>
+        <v>92957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135494430</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135522445</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>135494402</v>
       </c>
       <c r="B24" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>135494411</v>
       </c>
       <c r="B25" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>135494431</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>135522443</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>135494438</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>135522444</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>135522449</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135494429</v>
       </c>
       <c r="B31" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>135494393</v>
       </c>
       <c r="B32" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>135494406</v>
       </c>
       <c r="B33" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>135494409</v>
       </c>
       <c r="B34" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135494412</v>
       </c>
       <c r="B35" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>135494413</v>
       </c>
       <c r="B36" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>135494427</v>
       </c>
       <c r="B37" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>135494428</v>
       </c>
       <c r="B38" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>135522446</v>
       </c>
       <c r="B39" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135494432</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135494433</v>
       </c>
       <c r="B3" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135494436</v>
       </c>
       <c r="B4" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135494440</v>
       </c>
       <c r="B5" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135494391</v>
       </c>
       <c r="B6" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135494392</v>
       </c>
       <c r="B7" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135494394</v>
       </c>
       <c r="B8" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>135494395</v>
       </c>
       <c r="B9" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135494396</v>
       </c>
       <c r="B10" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>135494397</v>
       </c>
       <c r="B11" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>135494404</v>
       </c>
       <c r="B12" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135494405</v>
       </c>
       <c r="B13" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>135494408</v>
       </c>
       <c r="B14" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135494435</v>
       </c>
       <c r="B15" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135522442</v>
       </c>
       <c r="B16" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135522447</v>
       </c>
       <c r="B17" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135522448</v>
       </c>
       <c r="B18" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135494439</v>
       </c>
       <c r="B19" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>135522430</v>
       </c>
       <c r="B20" t="n">
-        <v>93325</v>
+        <v>93352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135494410</v>
       </c>
       <c r="B21" t="n">
-        <v>92957</v>
+        <v>92984</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135494430</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135522445</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>135494402</v>
       </c>
       <c r="B24" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>135494411</v>
       </c>
       <c r="B25" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>135494431</v>
       </c>
       <c r="B26" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>135522443</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135494429</v>
       </c>
       <c r="B31" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>135494393</v>
       </c>
       <c r="B32" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>135494406</v>
       </c>
       <c r="B33" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>135494409</v>
       </c>
       <c r="B34" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>135494412</v>
       </c>
       <c r="B35" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>135494413</v>
       </c>
       <c r="B36" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>135494427</v>
       </c>
       <c r="B37" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>135494428</v>
       </c>
       <c r="B38" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>135522446</v>
       </c>
       <c r="B39" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135494432</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135494433</v>
       </c>
       <c r="B3" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135494436</v>
       </c>
       <c r="B4" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135494440</v>
       </c>
       <c r="B5" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135494391</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135494392</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135494394</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>135494395</v>
       </c>
       <c r="B9" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135494396</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>135494397</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>135494404</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135494405</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>135494408</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>135494435</v>
       </c>
       <c r="B15" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135522442</v>
       </c>
       <c r="B16" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>135522447</v>
       </c>
       <c r="B17" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>135522448</v>
       </c>
       <c r="B18" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135494439</v>
       </c>
       <c r="B19" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>135522430</v>
       </c>
       <c r="B20" t="n">
-        <v>93357</v>
+        <v>93359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135494410</v>
       </c>
       <c r="B21" t="n">
-        <v>92989</v>
+        <v>92991</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135494429</v>
       </c>
       <c r="B31" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43065-2025 artfynd.xlsx
+++ b/artfynd/A 43065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3727,48 +3727,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135522444</v>
+        <v>136044719</v>
       </c>
       <c r="B29" t="n">
-        <v>58141</v>
+        <v>57169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vislakt, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>852196</v>
+        <v>852790</v>
       </c>
       <c r="R29" t="n">
-        <v>7375416</v>
+        <v>7375455</v>
       </c>
       <c r="S29" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,22 +3797,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,24 +3817,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522444</t>
+          <t>https://artportalen.se/Sighting/136044719</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135522449</v>
+        <v>135522444</v>
       </c>
       <c r="B30" t="n">
         <v>58141</v>
@@ -3874,13 +3869,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>852030</v>
+        <v>852196</v>
       </c>
       <c r="R30" t="n">
-        <v>7375425</v>
+        <v>7375416</v>
       </c>
       <c r="S30" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,38 +3940,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135522449</t>
+          <t>https://artportalen.se/Sighting/135522444</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135494429</v>
+        <v>135522449</v>
       </c>
       <c r="B31" t="n">
-        <v>98144</v>
+        <v>58141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,13 +3981,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>852147</v>
+        <v>852030</v>
       </c>
       <c r="R31" t="n">
-        <v>7375437</v>
+        <v>7375425</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4021,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,49 +4041,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494429</t>
+          <t>https://artportalen.se/Sighting/135522449</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135494393</v>
+        <v>135494429</v>
       </c>
       <c r="B32" t="n">
-        <v>79464</v>
+        <v>98144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,13 +4093,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>852762</v>
+        <v>852147</v>
       </c>
       <c r="R32" t="n">
-        <v>7375449</v>
+        <v>7375437</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4133,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4143,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,13 +4164,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494393</t>
+          <t>https://artportalen.se/Sighting/135494429</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135494406</v>
+        <v>135494393</v>
       </c>
       <c r="B33" t="n">
         <v>79464</v>
@@ -4210,13 +4205,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>852733</v>
+        <v>852762</v>
       </c>
       <c r="R33" t="n">
-        <v>7375489</v>
+        <v>7375449</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4245,7 +4240,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4255,7 +4250,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,13 +4276,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494406</t>
+          <t>https://artportalen.se/Sighting/135494393</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135494409</v>
+        <v>135494406</v>
       </c>
       <c r="B34" t="n">
         <v>79464</v>
@@ -4322,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>852761</v>
+        <v>852733</v>
       </c>
       <c r="R34" t="n">
-        <v>7375492</v>
+        <v>7375489</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4357,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4367,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,13 +4388,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494409</t>
+          <t>https://artportalen.se/Sighting/135494406</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135494412</v>
+        <v>135494409</v>
       </c>
       <c r="B35" t="n">
         <v>79464</v>
@@ -4434,13 +4429,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>852548</v>
+        <v>852761</v>
       </c>
       <c r="R35" t="n">
-        <v>7375432</v>
+        <v>7375492</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4469,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,13 +4500,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494412</t>
+          <t>https://artportalen.se/Sighting/135494409</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135494413</v>
+        <v>135494412</v>
       </c>
       <c r="B36" t="n">
         <v>79464</v>
@@ -4549,10 +4544,10 @@
         <v>852548</v>
       </c>
       <c r="R36" t="n">
-        <v>7375398</v>
+        <v>7375432</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4581,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,13 +4612,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494413</t>
+          <t>https://artportalen.se/Sighting/135494412</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135494427</v>
+        <v>135494413</v>
       </c>
       <c r="B37" t="n">
         <v>79464</v>
@@ -4658,13 +4653,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>852235</v>
+        <v>852548</v>
       </c>
       <c r="R37" t="n">
-        <v>7375410</v>
+        <v>7375398</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4693,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4703,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,13 +4724,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494427</t>
+          <t>https://artportalen.se/Sighting/135494413</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135494428</v>
+        <v>135494427</v>
       </c>
       <c r="B38" t="n">
         <v>79464</v>
@@ -4770,13 +4765,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>852154</v>
+        <v>852235</v>
       </c>
       <c r="R38" t="n">
-        <v>7375442</v>
+        <v>7375410</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4805,7 +4800,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4815,7 +4810,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,13 +4836,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494428</t>
+          <t>https://artportalen.se/Sighting/135494427</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135522446</v>
+        <v>135494428</v>
       </c>
       <c r="B39" t="n">
         <v>79464</v>
@@ -4882,13 +4877,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>852123</v>
+        <v>852154</v>
       </c>
       <c r="R39" t="n">
         <v>7375442</v>
       </c>
       <c r="S39" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4927,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,16 +4937,128 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494428</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135522446</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vislakt, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>852123</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7375442</v>
+      </c>
+      <c r="S40" t="n">
+        <v>68</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135522446</t>
         </is>
@@ -4997,6 +5104,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
